--- a/data.mn/public/datasets/mongolbank-exchange-rates-monthly-major.xlsx
+++ b/data.mn/public/datasets/mongolbank-exchange-rates-monthly-major.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,6 +416,17 @@
   </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -480,7 +491,7 @@
         <v>493.1622</v>
       </c>
       <c r="I2" t="n">
-        <v>513.2415</v>
+        <v>522.8231</v>
       </c>
     </row>
     <row r="3">
@@ -513,7 +524,7 @@
         <v>4006.7397</v>
       </c>
       <c r="I3" t="n">
-        <v>4200.647</v>
+        <v>4157.0142</v>
       </c>
     </row>
     <row r="4">
@@ -546,7 +557,7 @@
         <v>23.7133</v>
       </c>
       <c r="I4" t="n">
-        <v>22.869</v>
+        <v>22.5261</v>
       </c>
     </row>
     <row r="5">
@@ -579,7 +590,7 @@
         <v>2.4951</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4549</v>
+        <v>2.4252</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +623,7 @@
         <v>42.6125</v>
       </c>
       <c r="I6" t="n">
-        <v>46.0132</v>
+        <v>46.2154</v>
       </c>
     </row>
     <row r="7">
@@ -645,7 +656,7 @@
         <v>3544.864</v>
       </c>
       <c r="I7" t="n">
-        <v>3563.2438</v>
+        <v>3574.939</v>
       </c>
     </row>
   </sheetData>
@@ -661,6 +672,17 @@
   </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -725,7 +747,7 @@
         <v>493.1622</v>
       </c>
       <c r="I2" t="n">
-        <v>513.2415</v>
+        <v>522.8231</v>
       </c>
     </row>
     <row r="3">
@@ -758,7 +780,7 @@
         <v>4006.7397</v>
       </c>
       <c r="I3" t="n">
-        <v>4200.647</v>
+        <v>4157.0142</v>
       </c>
     </row>
     <row r="4">
@@ -791,7 +813,7 @@
         <v>23.7133</v>
       </c>
       <c r="I4" t="n">
-        <v>22.869</v>
+        <v>22.5261</v>
       </c>
     </row>
     <row r="5">
@@ -824,7 +846,7 @@
         <v>2.4951</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4549</v>
+        <v>2.4252</v>
       </c>
     </row>
     <row r="6">
@@ -857,7 +879,7 @@
         <v>42.6125</v>
       </c>
       <c r="I6" t="n">
-        <v>46.0132</v>
+        <v>46.2154</v>
       </c>
     </row>
     <row r="7">
@@ -890,7 +912,7 @@
         <v>3544.864</v>
       </c>
       <c r="I7" t="n">
-        <v>3563.2438</v>
+        <v>3574.939</v>
       </c>
     </row>
   </sheetData>
